--- a/output/pdf_financials_xlsx/CNVI.xlsx
+++ b/output/pdf_financials_xlsx/CNVI.xlsx
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>25.469</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>32.306</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>3.289</v>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>25.469</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>32.306</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>3.289</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>26.948</v>
+        <v>1.479</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>35.382</v>
+        <v>3.076</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>1.747</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">

--- a/output/pdf_financials_xlsx/CNVI.xlsx
+++ b/output/pdf_financials_xlsx/CNVI.xlsx
@@ -4063,10 +4063,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>5.999</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="65">
@@ -4345,16 +4345,16 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="71">
@@ -4393,16 +4393,16 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="72">
@@ -4585,16 +4585,16 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>38.368</v>
+        <v>38.202</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>4.07</v>
+        <v>3.724</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.761</v>
+        <v>0.375</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.491</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="76">
@@ -4741,16 +4741,16 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>0.751</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>0.981</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>1.323</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="79">
@@ -4789,16 +4789,16 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0</v>
+        <v>0.751</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0</v>
+        <v>0.981</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>1.323</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="80">
@@ -4852,25 +4852,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K80" s="3" t="n">
+        <v>-0.06640596712289087</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.03759952398492619</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>-0.5401390644753477</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.2764890282131661</v>
       </c>
     </row>
     <row r="81">
@@ -5101,16 +5093,16 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.751</v>
+        <v>0</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1.037</v>
+        <v>0.056</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>1.323</v>
+        <v>0</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0.856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6149,19 +6141,19 @@
         <v>1.439352</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>5.133</v>
+        <v>6.784</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>8.119</v>
+        <v>12.155</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>5.079</v>
+        <v>9.162000000000001</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="108">
@@ -8245,7 +8237,11 @@
           <t>Current portion of lease obligations 6</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -8654,7 +8650,11 @@
           <t>Lease obligations 6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11443,7 +11443,11 @@
           <t>Current portion of lease obligations 5</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -11763,7 +11767,11 @@
           <t>Lease obligations 5</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -29011,7 +29019,11 @@
           <t>Share-based compensation expense 13</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -29574,7 +29586,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -32241,7 +32257,11 @@
           <t>Share-based compensation expense 11</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -35605,7 +35625,11 @@
           <t>Share-based compensation expense 12</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -35759,7 +35783,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
